--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:06</t>
+    <t xml:space="preserve">2026-09-09 22:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:59</t>
+    <t xml:space="preserve">2026-09-17 13:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:57</t>
+    <t xml:space="preserve">2026-09-23 12:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:26</t>
+    <t xml:space="preserve">2026-10-02 13:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2018_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2018_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:15</t>
+    <t xml:space="preserve">2026-10-05 09:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -576,7 +576,7 @@
         <v>2018</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>842480.62</v>
+        <v>842480.63</v>
       </c>
     </row>
     <row r="7">
@@ -610,7 +610,7 @@
         <v>2018</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>725759.12</v>
+        <v>725759.13</v>
       </c>
     </row>
     <row r="9">
